--- a/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,13</t>
+          <t>-6,9; 1,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 2,42</t>
+          <t>-12,58; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 3,14</t>
+          <t>-15,86; 3,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-90,66; 79,13</t>
+          <t>-91,31; 58,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 18,08</t>
+          <t>-54,92; 10,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,43; 96,65</t>
+          <t>-87,06; 128,23</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,04</t>
+          <t>-2,26; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 3,81</t>
+          <t>-7,18; 3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 13,44</t>
+          <t>-2,36; 13,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 188,24</t>
+          <t>-60,4; 236,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 32,63</t>
+          <t>-43,53; 31,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 150,82</t>
+          <t>-22,3; 161,49</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 5,81</t>
+          <t>-2,51; 5,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 1,31</t>
+          <t>-12,41; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 4,86</t>
+          <t>-15,15; 5,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 173,51</t>
+          <t>-37,65; 177,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 8,07</t>
+          <t>-48,19; 10,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 23,16</t>
+          <t>-50,19; 29,66</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,84</t>
+          <t>-3,28; 3,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 7,25</t>
+          <t>-1,74; 7,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,9</t>
+          <t>-8,85; 2,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 175,03</t>
+          <t>-63,46; 172,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 146,91</t>
+          <t>-23,0; 137,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 36,36</t>
+          <t>-58,13; 38,33</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,19</t>
+          <t>-4,98; 1,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,53</t>
+          <t>-4,57; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 55,38</t>
+          <t>-38,37; 55,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 8,85</t>
+          <t>-30,4; 9,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 30,14</t>
+          <t>-29,15; 28,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,09</t>
+          <t>-6,96; 1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 1,46</t>
+          <t>-11,52; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 3,99</t>
+          <t>-15,04; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 58,92</t>
+          <t>-90,14; 83,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 10,85</t>
+          <t>-53,22; 17,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 128,23</t>
+          <t>-87,39; 101,0</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,1</t>
+          <t>-1,9; 3,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 3,64</t>
+          <t>-6,94; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 13,37</t>
+          <t>-2,03; 13,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 236,83</t>
+          <t>-53,16; 233,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 31,44</t>
+          <t>-41,52; 31,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 161,49</t>
+          <t>-18,41; 140,87</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,75</t>
+          <t>-2,56; 5,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 1,99</t>
+          <t>-12,52; 0,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 5,94</t>
+          <t>-14,19; 6,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 177,95</t>
+          <t>-39,29; 159,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 10,98</t>
+          <t>-47,57; 5,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 29,66</t>
+          <t>-49,86; 29,54</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,73</t>
+          <t>-3,46; 3,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,67</t>
+          <t>-1,84; 7,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 2,83</t>
+          <t>-8,54; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 172,73</t>
+          <t>-62,82; 167,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 137,53</t>
+          <t>-20,15; 145,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 38,33</t>
+          <t>-56,75; 31,09</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,79; 1,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,24</t>
+          <t>-4,82; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,53</t>
+          <t>-4,43; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 55,49</t>
+          <t>-36,55; 51,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,73</t>
+          <t>-28,7; 7,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 28,82</t>
+          <t>-28,99; 30,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Habitat-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,09%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,15</t>
+          <t>-6,72; 1,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 2,79</t>
+          <t>-12,65; 2,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 3,56</t>
+          <t>-4,06; 5,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-90,14; 83,67</t>
+          <t>-90,66; 79,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 17,93</t>
+          <t>-55,75; 18,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 101,0</t>
+          <t>-56,84; 240,54</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,52</t>
+          <t>-2,0; 3,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 3,65</t>
+          <t>-7,26; 3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 13,35</t>
+          <t>-3,39; 6,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 233,89</t>
+          <t>-57,63; 188,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 31,4</t>
+          <t>-40,98; 32,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 140,87</t>
+          <t>-29,12; 87,4</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,87</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,5%</t>
+          <t>-5,28%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,4</t>
+          <t>-3,05; 5,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 0,75</t>
+          <t>-12,68; 1,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 6,33</t>
+          <t>-10,18; 6,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,29; 159,27</t>
+          <t>-44,17; 173,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 5,78</t>
+          <t>-49,4; 8,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 29,54</t>
+          <t>-37,49; 32,07</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,1%</t>
+          <t>-19,89%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,64</t>
+          <t>-3,4; 3,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 7,7</t>
+          <t>-1,94; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,4</t>
+          <t>-7,99; 3,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,82; 167,39</t>
+          <t>-61,47; 175,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 145,95</t>
+          <t>-20,66; 146,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 31,09</t>
+          <t>-55,05; 40,77</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-2,77%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,6</t>
+          <t>-1,89; 1,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,08</t>
+          <t>-4,68; 1,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,62</t>
+          <t>-3,45; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 51,7</t>
+          <t>-36,56; 55,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 7,65</t>
+          <t>-28,75; 8,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 30,35</t>
+          <t>-24,45; 26,1</t>
         </is>
       </c>
     </row>
